--- a/AQD R3 DDBB views 2026.xlsx
+++ b/AQD R3 DDBB views 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bm365s.sharepoint.com/sites/Dataflowsviewers-TEAM/Documentos compartidos/01 Dataflows/AQD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="11_C639A3DEA6208F4D3E5BE6FD81B4B2AD62CC9A9E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B33268C7-BE1A-4539-A3C4-00ECA11F5E83}"/>
+  <xr:revisionPtr revIDLastSave="235" documentId="11_C639A3DEA6208F4D3E5BE6FD81B4B2AD62CC9A9E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDD14EB8-6DFE-4FE8-8A0B-58AF7126EBA7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SamplingProcess (SPP)" sheetId="1" r:id="rId1"/>
@@ -259,7 +259,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="586">
   <si>
     <t>2026 task</t>
   </si>
@@ -2057,49 +2057,6 @@
     <t>Task #304741 ARZ_01_A Check country code</t>
   </si>
   <si>
-    <r>
-      <t>The value reported under </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>CountryCode</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t> in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>AssessmentRegimeZone</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t> table shall identify the reporting country or territory using a valid ISO2 country code.</t>
-    </r>
-  </si>
-  <si>
     <t>Done</t>
   </si>
   <si>
@@ -2112,193 +2069,16 @@
     <t>Task #304742 ARZ_02_A AssessmentRegimeId</t>
   </si>
   <si>
-    <r>
-      <t>The value reported under </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>AssessmentRegimeId</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t> in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>AssessmentRegimeZone</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t> table shall uniquely identify an assessment regime within the reporting country.</t>
-    </r>
-  </si>
-  <si>
     <t>Task #304743 ARZ_02_B AssessmentRegimeId</t>
   </si>
   <si>
-    <r>
-      <t>The value reported under </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>AssessmentRegimeId</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t> in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>AssessmentRegimeZone</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t> table should follow a consistent naming convention for assessment regime identifiers.</t>
-    </r>
-  </si>
-  <si>
     <t>Task #304744 ARZ_02_C AssessmentRegimeId</t>
   </si>
   <si>
-    <r>
-      <t>The combination of </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>PollutantId</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t> and environmental objective reported in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>AssessmentRegimeZone</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t> table shall correspond to a valid combination defined in the environmental objective reference vocabulary.</t>
-    </r>
-  </si>
-  <si>
     <t>Task #304745 ARZ_02_D AssessmentRegimeId</t>
   </si>
   <si>
-    <r>
-      <t>The value reported under </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>AssessmentRegimeId</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t> shall uniquely identify a single environmental objective across the reference dataset.</t>
-    </r>
-  </si>
-  <si>
     <t>Task #304746 ARZ_02_E AssessmentRegimeId</t>
-  </si>
-  <si>
-    <r>
-      <t>Within the current R3 submission, the value reported under </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>AssessmentRegimeId</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t> shall uniquely identify one assessment regime for a specific zone and environmental objective.</t>
-    </r>
   </si>
   <si>
     <t>Task #304914 ARZ_02_F AssessmentRegimeId</t>
@@ -3047,16 +2827,1127 @@
   <si>
     <t>https://taskman.eionet.europa.eu/issues/304911</t>
   </si>
+  <si>
+    <t>The sum of the areas of the different zones, grouped by PollutantId, ProtectionTarget, ObjectiveType and ReportingMetric, when ProtectionTarget = Health, must be within ±0.5% of the country surface area.</t>
+  </si>
+  <si>
+    <t>ZoneName must be consistent across records with the same ZoneId, both within the current delivery and against the reference dataset.</t>
+  </si>
+  <si>
+    <t>PollutantId must correspond to a pollutant for which assessment regime reporting is defined in the Environmental Objective vocabulary.</t>
+  </si>
+  <si>
+    <t>The sum of the resident population reported for zones, grouped by expected PollutantId and ProtectionTarget combinations, shall be within ±5% of the reference population.</t>
+  </si>
+  <si>
+    <t>The reported resident population should be consistent with the population previously reported for the same zone, taking into account the reference year of the population data.</t>
+  </si>
+  <si>
+    <r>
+      <t>The value reported under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t>CountryCode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t> in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t>AssessmentRegimeZone</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t> table shall identify the reporting country or territory using a valid ISO2 country code.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The value reported under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t>AssessmentRegimeId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t> in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t>AssessmentRegimeZone</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t> table shall uniquely identify an assessment regime within the reporting country.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The value reported under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t>AssessmentRegimeId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t> in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t>AssessmentRegimeZone</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t> table should follow a consistent naming convention for assessment regime identifiers.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The combination of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t>PollutantId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t> and environmental objective reported in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t>AssessmentRegimeZone</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t> table shall correspond to a valid combination defined in the environmental objective reference vocabulary.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The value reported under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t>AssessmentRegimeId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t> shall uniquely identify a single environmental objective across the reference dataset.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Within the current R3 submission, the value reported under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t>AssessmentRegimeId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Verdana"/>
+      </rPr>
+      <t> shall uniquely identify one assessment regime for a specific zone and environmental objective.</t>
+    </r>
+  </si>
+  <si>
+    <t>"Any substantial increase or decrease in population is supported by an updated population reference year or other plausible explanation", what increase/decrease %?</t>
+  </si>
+  <si>
+    <t>need clarifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> {%R3_COUNTRY_CODE%}</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>USE [Airquality_R3];
+GO
+/* ============================================================
+   ZOG_02_B
+   Returns records from reporting.ZoneGeometry whose ZoneId does
+   NOT follow the recommended naming convention:
+       ZON{separator}{CountryCode}[optional suffix]
+   Allowed separators: '.', '_' or '-'.
+   Valid examples for CountryCode = ES:
+       ZON_ES
+       ZON-ES
+       ZON.ES
+       ZON_ES0835
+   ============================================================ */
+CREATE OR ALTER VIEW [qc].[ZOG_02_B]
+AS
+WITH CTE_Zone AS
+(
+    SELECT
+        /* Keep the original value to identify leading/trailing spaces. */
+        zg.ZoneId AS ZoneIdRaw,
+        /* Trim ZoneId; convert an empty value to NULL. */
+        NULLIF(LTRIM(RTRIM(zg.ZoneId)), '') AS ZoneId,
+        /* Trim CountryCode; convert an empty value to NULL. */
+        NULLIF(LTRIM(RTRIM(zg.CountryCode)), '') AS CountryCode,
+        /* Identify ZoneId values with leading or trailing spaces. */
+        CASE
+            WHEN zg.ZoneId IS NULL THEN 0
+            WHEN zg.ZoneId &lt;&gt; LTRIM(RTRIM(zg.ZoneId)) THEN 1
+            ELSE 0
+        END AS HasLeadingOrTrailingSpaces
+    FROM [reporting].[ZoneGeometry] AS zg
+),
+CTE_Countries AS
+(
+    /* Use the reference vocabulary as the canonical ISO country-code source. */
+    SELECT DISTINCT
+        UPPER(LTRIM(RTRIM(v.Notation))) AS CountryCode
+    FROM [reference].[Vocabulary] AS v
+    WHERE v.Vocabulary = 'countries'
+      AND NULLIF(LTRIM(RTRIM(v.Notation)), '') IS NOT NULL
+)
+SELECT
+    z.ZoneId,
+    z.CountryCode
+FROM CTE_Zone AS z
+WHERE
+    /* ZoneId is missing, empty, or has leading/trailing spaces. */
+    z.ZoneIdRaw IS NULL
+    OR z.ZoneId IS NULL
+    OR z.HasLeadingOrTrailingSpaces = 1
+    /* CountryCode is missing. */
+    OR z.CountryCode IS NULL
+    /* CountryCode does not exist in the reference vocabulary. */
+    OR NOT EXISTS
+    (
+        SELECT 1
+        FROM CTE_Countries AS c
+        WHERE c.CountryCode COLLATE Latin1_General_BIN2 =
+              z.CountryCode COLLATE Latin1_General_BIN2
+    )
+    /* ZoneId does not comply with ZON{separator}{CountryCode}[optional suffix]. */
+    OR NOT
+    (
+        /* Minimum length: ZON + separator + CountryCode. */
+        LEN(z.ZoneId) &gt;= 6
+        /* Prefix must be exactly ZON and is case-sensitive. */
+        AND LEFT(z.ZoneId COLLATE Latin1_General_BIN2, 3) = 'ZON'
+        /* The separator must be '.', '_' or '-'. */
+        AND SUBSTRING(z.ZoneId, 4, 1) IN ('.', '_', '-')
+        /* The embedded CountryCode must contain two uppercase letters. */
+        AND SUBSTRING(z.ZoneId COLLATE Latin1_General_BIN2, 5, 2)
+            LIKE '[A-Z][A-Z]'
+        /* The embedded CountryCode must match the reported CountryCode. */
+        AND SUBSTRING(z.ZoneId COLLATE Latin1_General_BIN2, 5, 2) =
+            z.CountryCode COLLATE Latin1_General_BIN2
+    );</t>
+  </si>
+  <si>
+    <t>ZOG_02_B ZoneId correction</t>
+  </si>
+  <si>
+    <t>USE [Airquality_R3];
+GO
+/* ============================================================
+   ZOG_02_B_TEST
+   Returns records from qctesting.ZoneGeometry whose ZoneId does
+   NOT follow the recommended naming convention:
+       ZON{separator}{CountryCode}[optional suffix]
+   Allowed separators: '.', '_' or '-'.
+   Valid examples for CountryCode = ES:
+       ZON_ES
+       ZON-ES
+       ZON.ES
+       ZON_ES0835
+   ============================================================ */
+CREATE OR ALTER VIEW [qctesting].[ZOG_02_B_TEST]
+AS
+WITH CTE_Zone AS
+(
+    SELECT
+        /* Keep the original value to identify leading/trailing spaces. */
+        zg.ZoneId AS ZoneIdRaw,
+        /* Trim ZoneId; convert an empty value to NULL. */
+        NULLIF(LTRIM(RTRIM(zg.ZoneId)), '') AS ZoneId,
+        /* Trim CountryCode; convert an empty value to NULL. */
+        NULLIF(LTRIM(RTRIM(zg.CountryCode)), '') AS CountryCode,
+        /* Identify ZoneId values with leading or trailing spaces. */
+        CASE
+            WHEN zg.ZoneId IS NULL THEN 0
+            WHEN zg.ZoneId &lt;&gt; LTRIM(RTRIM(zg.ZoneId)) THEN 1
+            ELSE 0
+        END AS HasLeadingOrTrailingSpaces
+    FROM [qctesting].[ZoneGeometry] AS zg
+),
+CTE_Countries AS
+(
+    /* Use the reference vocabulary as the canonical ISO country-code source. */
+    SELECT DISTINCT
+        UPPER(LTRIM(RTRIM(v.Notation))) AS CountryCode
+    FROM [reference].[Vocabulary] AS v
+    WHERE v.Vocabulary = 'countries'
+      AND NULLIF(LTRIM(RTRIM(v.Notation)), '') IS NOT NULL
+)
+SELECT
+    z.ZoneId,
+    z.CountryCode
+FROM CTE_Zone AS z
+WHERE
+    /* ZoneId is missing, empty, or has leading/trailing spaces. */
+    z.ZoneIdRaw IS NULL
+    OR z.ZoneId IS NULL
+    OR z.HasLeadingOrTrailingSpaces = 1
+    /* CountryCode is missing. */
+    OR z.CountryCode IS NULL
+    /* CountryCode does not exist in the reference vocabulary. */
+    OR NOT EXISTS
+    (
+        SELECT 1
+        FROM CTE_Countries AS c
+        WHERE c.CountryCode COLLATE Latin1_General_BIN2 =
+              z.CountryCode COLLATE Latin1_General_BIN2
+    )
+    /* ZoneId does not comply with ZON{separator}{CountryCode}[optional suffix]. */
+    OR NOT
+    (
+        /* Minimum length: ZON + separator + CountryCode. */
+        LEN(z.ZoneId) &gt;= 6
+        /* Prefix must be exactly ZON and is case-sensitive. */
+        AND LEFT(z.ZoneId COLLATE Latin1_General_BIN2, 3) = 'ZON'
+        /* The separator must be '.', '_' or '-'. */
+        AND SUBSTRING(z.ZoneId, 4, 1) IN ('.', '_', '-')
+        /* The embedded CountryCode must contain two uppercase letters. */
+        AND SUBSTRING(z.ZoneId COLLATE Latin1_General_BIN2, 5, 2)
+            LIKE '[A-Z][A-Z]'
+        /* The embedded CountryCode must match the reported CountryCode. */
+        AND SUBSTRING(z.ZoneId COLLATE Latin1_General_BIN2, 5, 2) =
+            z.CountryCode COLLATE Latin1_General_BIN2
+    );
+GO</t>
+  </si>
+  <si>
+    <t>ZOG_02_B_TEST ZoneId correction</t>
+  </si>
+  <si>
+    <t>USE [Airquality_R3];
+GO
+SET ANSI_NULLS ON;
+GO
+SET QUOTED_IDENTIFIER ON;
+GO
+CREATE OR ALTER VIEW [qc].[ARZ_02_B]
+AS
+/* ============================================================
+   QC rule code: ARZ_02_B
+   QC rule name: Naming convention validation - AssessmentRegimeId
+   Returns AssessmentRegimeZone records whose AssessmentRegimeId
+   does not comply with the recommended identifier convention:
+       ARE_{ZoneId}_{PollutantId}_{ObjectiveType}_{ProtectionTarget}_
+       {ReportingMetric}_{ClassificationYear}[_{Index}]
+   Validation approach:
+   - The expected identifier is built from the attribute values
+     reported in the same record.
+   - ZoneId is not parsed from AssessmentRegimeId because it may
+     itself contain underscore characters.
+   - PollutantId is represented using exactly four digits.
+   - ClassificationYear is represented using exactly four digits.
+   - Index is optional and, when reported, must contain one character.
+   - Literal component values such as 'NA' are valid and are compared
+     exactly as reported.
+   - Records with missing or invalid components are excluded from this
+     naming-convention rule. They must be validated by the respective
+     attribute-level QC rules.
+   - Missing or empty AssessmentRegimeId values are validated by
+     ARZ_02_A.
+   ============================================================ */
+WITH CTE_source AS
+(
+    SELECT
+        arz.[CountryCode] COLLATE Latin1_General_CI_AS AS [CountryCode],
+        arz.[AssessmentRegimeId] COLLATE Latin1_General_CI_AS
+            AS [AssessmentRegimeIdRaw],
+        arz.[ZoneId] COLLATE Latin1_General_CI_AS AS [ZoneId],
+        arz.[PollutantId] AS [PollutantId],
+        CONVERT(NVARCHAR(100), arz.[ObjectiveType])
+            COLLATE Latin1_General_CI_AS AS [ObjectiveType],
+        CONVERT(NVARCHAR(100), arz.[ProtectionTarget])
+            COLLATE Latin1_General_CI_AS AS [ProtectionTarget],
+        CONVERT(NVARCHAR(100), arz.[ReportingMetric])
+            COLLATE Latin1_General_CI_AS AS [ReportingMetric],
+        arz.[ClassificationYear] AS [ClassificationYear],
+        /* Normalize AssessmentRegimeId for validation purposes. */
+        NULLIF
+        (
+            LTRIM(RTRIM(arz.[AssessmentRegimeId]))
+                COLLATE Latin1_General_CI_AS,
+            N''
+        ) COLLATE Latin1_General_CI_AS AS [AssessmentRegimeId],
+        /* Normalize identifier components. */
+        NULLIF
+        (
+            LTRIM(RTRIM(arz.[ZoneId]))
+                COLLATE Latin1_General_CI_AS,
+            N''
+        ) COLLATE Latin1_General_CI_AS AS [ZoneIdNormalized],
+        NULLIF
+        (
+            LTRIM(RTRIM(CONVERT(NVARCHAR(100), arz.[ObjectiveType])))
+                COLLATE Latin1_General_CI_AS,
+            N''
+        ) COLLATE Latin1_General_CI_AS AS [ObjectiveTypeNormalized],
+        NULLIF
+        (
+            LTRIM(RTRIM(CONVERT(NVARCHAR(100), arz.[ProtectionTarget])))
+                COLLATE Latin1_General_CI_AS,
+            N''
+        ) COLLATE Latin1_General_CI_AS AS [ProtectionTargetNormalized],
+        NULLIF
+        (
+            LTRIM(RTRIM(CONVERT(NVARCHAR(100), arz.[ReportingMetric])))
+                COLLATE Latin1_General_CI_AS,
+            N''
+        ) COLLATE Latin1_General_CI_AS AS [ReportingMetricNormalized],
+        TRY_CONVERT(INT, arz.[PollutantId]) AS [PollutantIdNumeric],
+        TRY_CONVERT(INT, arz.[ClassificationYear])
+            AS [ClassificationYearNumeric]
+    FROM [reporting].[AssessmentRegimeZone] AS arz
+),
+CTE_expected_identifier AS
+(
+    SELECT
+        s.*,
+        CASE
+            /* Build the expected identifier only when all required
+               source components are available and valid. */
+            WHEN s.[ZoneIdNormalized] IS NOT NULL
+             AND s.[PollutantIdNumeric] BETWEEN 0 AND 9999
+             AND s.[ObjectiveTypeNormalized] IS NOT NULL
+             AND s.[ProtectionTargetNormalized] IS NOT NULL
+             AND s.[ReportingMetricNormalized] IS NOT NULL
+             AND s.[ClassificationYearNumeric] BETWEEN 1000 AND 9999
+            THEN
+                CONCAT
+                (
+                    N'ARE_',
+                    s.[ZoneIdNormalized],
+                    N'_',
+                    RIGHT
+                    (
+                        N'0000' + CONVERT(NVARCHAR(4), s.[PollutantIdNumeric]),
+                        4
+                    ),
+                    N'_',
+                    s.[ObjectiveTypeNormalized],
+                    N'_',
+                    s.[ProtectionTargetNormalized],
+                    N'_',
+                    s.[ReportingMetricNormalized],
+                    N'_',
+                    CONVERT(NVARCHAR(4), s.[ClassificationYearNumeric])
+                ) COLLATE Latin1_General_CI_AS
+            ELSE NULL
+        END AS [ExpectedAssessmentRegimeId]
+    FROM CTE_source AS s
+),
+CTE_validation AS
+(
+    SELECT
+        e.*,
+        CASE
+            /* The identifier exactly matches the recommended base structure. */
+            WHEN e.[AssessmentRegimeId] = e.[ExpectedAssessmentRegimeId]
+                THEN 1
+            /* The identifier matches the base structure followed by
+               _{Index}, where Index contains exactly one character. */
+            WHEN LEN(e.[AssessmentRegimeId])
+                 = LEN(e.[ExpectedAssessmentRegimeId]) + 2
+             AND LEFT
+                 (
+                     e.[AssessmentRegimeId],
+                     LEN(e.[ExpectedAssessmentRegimeId])
+                 ) = e.[ExpectedAssessmentRegimeId]
+             AND SUBSTRING
+                 (
+                     e.[AssessmentRegimeId],
+                     LEN(e.[ExpectedAssessmentRegimeId]) + 1,
+                     1
+                 ) = N'_'
+                THEN 1
+            ELSE 0
+        END AS [IsValidAssessmentRegimeId]
+    FROM CTE_expected_identifier AS e
+)
+SELECT
+    [CountryCode],
+    [AssessmentRegimeIdRaw] AS [AssessmentRegimeId],
+    [ZoneId],
+    [PollutantId],
+    [ObjectiveType],
+    [ProtectionTarget],
+    [ReportingMetric],
+    [ClassificationYear],
+    [ExpectedAssessmentRegimeId],
+    'INVALID_ASSESSMENTREGIMEID_NAMING_CONVENTION' AS [QC_FailureReason]
+FROM CTE_validation
+WHERE
+    /* Missing or empty AssessmentRegimeId is handled by ARZ_02_A. */
+    [AssessmentRegimeId] IS NOT NULL
+    /* Missing or invalid components are handled by their respective
+       attribute-level QC rules. */
+    AND [ExpectedAssessmentRegimeId] IS NOT NULL
+    /* Return only actual naming-convention failures. */
+    AND [IsValidAssessmentRegimeId] = 0;
+GO</t>
+  </si>
+  <si>
+    <t>[ARZ_02_B] correction</t>
+  </si>
+  <si>
+    <t>USE [Airquality_R3];
+GO
+SET ANSI_NULLS ON;
+GO
+SET QUOTED_IDENTIFIER ON;
+GO
+CREATE OR ALTER VIEW [qctesting].[ARZ_02_B_TEST]
+AS
+/* ============================================================
+   QC rule code: ARZ_02_B
+   QC rule name: Naming convention validation - AssessmentRegimeId
+   Testing version of qc.ARZ_02_B.
+   Test data source:
+       qctesting.AssessmentRegimeZone
+   Returns records whose AssessmentRegimeId does not comply with:
+       ARE_{ZoneId}_{PollutantId}_{ObjectiveType}_{ProtectionTarget}_
+       {ReportingMetric}_{ClassificationYear}[_{Index}]
+   Validation approach:
+   - The expected identifier is built from the attribute values
+     reported in the same record.
+   - ZoneId is not parsed from AssessmentRegimeId because it may
+     itself contain underscore characters.
+   - PollutantId is represented using exactly four digits.
+   - ClassificationYear is represented using exactly four digits.
+   - Index is optional and, when reported, must contain one character.
+   - Literal component values such as 'NA' are valid and are compared
+     exactly as reported.
+   - Records with missing or invalid components are excluded from this
+     naming-convention rule. They must be validated by the respective
+     attribute-level QC rules.
+   - Missing or empty AssessmentRegimeId values are validated by
+     ARZ_02_A.
+   ============================================================ */
+WITH CTE_source AS
+(
+    SELECT
+        arz.[CountryCode] COLLATE Latin1_General_CI_AS AS [CountryCode],
+        arz.[AssessmentRegimeId] COLLATE Latin1_General_CI_AS
+            AS [AssessmentRegimeIdRaw],
+        arz.[ZoneId] COLLATE Latin1_General_CI_AS AS [ZoneId],
+        arz.[PollutantId] AS [PollutantId],
+        CONVERT(NVARCHAR(100), arz.[ObjectiveType])
+            COLLATE Latin1_General_CI_AS AS [ObjectiveType],
+        CONVERT(NVARCHAR(100), arz.[ProtectionTarget])
+            COLLATE Latin1_General_CI_AS AS [ProtectionTarget],
+        CONVERT(NVARCHAR(100), arz.[ReportingMetric])
+            COLLATE Latin1_General_CI_AS AS [ReportingMetric],
+        arz.[ClassificationYear] AS [ClassificationYear],
+        /* Normalize AssessmentRegimeId for validation purposes. */
+        NULLIF
+        (
+            LTRIM(RTRIM(arz.[AssessmentRegimeId]))
+                COLLATE Latin1_General_CI_AS,
+            N''
+        ) COLLATE Latin1_General_CI_AS AS [AssessmentRegimeId],
+        /* Normalize identifier components. */
+        NULLIF
+        (
+            LTRIM(RTRIM(arz.[ZoneId]))
+                COLLATE Latin1_General_CI_AS,
+            N''
+        ) COLLATE Latin1_General_CI_AS AS [ZoneIdNormalized],
+        NULLIF
+        (
+            LTRIM(RTRIM(CONVERT(NVARCHAR(100), arz.[ObjectiveType])))
+                COLLATE Latin1_General_CI_AS,
+            N''
+        ) COLLATE Latin1_General_CI_AS AS [ObjectiveTypeNormalized],
+        NULLIF
+        (
+            LTRIM(RTRIM(CONVERT(NVARCHAR(100), arz.[ProtectionTarget])))
+                COLLATE Latin1_General_CI_AS,
+            N''
+        ) COLLATE Latin1_General_CI_AS AS [ProtectionTargetNormalized],
+        NULLIF
+        (
+            LTRIM(RTRIM(CONVERT(NVARCHAR(100), arz.[ReportingMetric])))
+                COLLATE Latin1_General_CI_AS,
+            N''
+        ) COLLATE Latin1_General_CI_AS AS [ReportingMetricNormalized],
+        TRY_CONVERT(INT, arz.[PollutantId]) AS [PollutantIdNumeric],
+        TRY_CONVERT(INT, arz.[ClassificationYear])
+            AS [ClassificationYearNumeric]
+    FROM [qctesting].[AssessmentRegimeZone] AS arz
+),
+CTE_expected_identifier AS
+(
+    SELECT
+        s.*,
+        CASE
+            /* Build the expected identifier only when all required
+               source components are available and valid. */
+            WHEN s.[ZoneIdNormalized] IS NOT NULL
+             AND s.[PollutantIdNumeric] BETWEEN 0 AND 9999
+             AND s.[ObjectiveTypeNormalized] IS NOT NULL
+             AND s.[ProtectionTargetNormalized] IS NOT NULL
+             AND s.[ReportingMetricNormalized] IS NOT NULL
+             AND s.[ClassificationYearNumeric] BETWEEN 1000 AND 9999
+            THEN
+                CONCAT
+                (
+                    N'ARE_',
+                    s.[ZoneIdNormalized],
+                    N'_',
+                    RIGHT
+                    (
+                        N'0000' + CONVERT(NVARCHAR(4), s.[PollutantIdNumeric]),
+                        4
+                    ),
+                    N'_',
+                    s.[ObjectiveTypeNormalized],
+                    N'_',
+                    s.[ProtectionTargetNormalized],
+                    N'_',
+                    s.[ReportingMetricNormalized],
+                    N'_',
+                    CONVERT(NVARCHAR(4), s.[ClassificationYearNumeric])
+                ) COLLATE Latin1_General_CI_AS
+            ELSE NULL
+        END AS [ExpectedAssessmentRegimeId]
+    FROM CTE_source AS s
+),
+CTE_validation AS
+(
+    SELECT
+        e.*,
+        CASE
+            /* The identifier exactly matches the recommended base structure. */
+            WHEN e.[AssessmentRegimeId] = e.[ExpectedAssessmentRegimeId]
+                THEN 1
+            /* The identifier matches the base structure followed by
+               _{Index}, where Index contains exactly one character. */
+            WHEN LEN(e.[AssessmentRegimeId])
+                 = LEN(e.[ExpectedAssessmentRegimeId]) + 2
+             AND LEFT
+                 (
+                     e.[AssessmentRegimeId],
+                     LEN(e.[ExpectedAssessmentRegimeId])
+                 ) = e.[ExpectedAssessmentRegimeId]
+             AND SUBSTRING
+                 (
+                     e.[AssessmentRegimeId],
+                     LEN(e.[ExpectedAssessmentRegimeId]) + 1,
+                     1
+                 ) = N'_'
+                THEN 1
+            ELSE 0
+        END AS [IsValidAssessmentRegimeId]
+    FROM CTE_expected_identifier AS e
+)
+SELECT
+    [CountryCode],
+    [AssessmentRegimeIdRaw] AS [AssessmentRegimeId],
+    [ZoneId],
+    [PollutantId],
+    [ObjectiveType],
+    [ProtectionTarget],
+    [ReportingMetric],
+    [ClassificationYear],
+    [ExpectedAssessmentRegimeId],
+    'INVALID_ASSESSMENTREGIMEID_NAMING_CONVENTION' AS [QC_FailureReason]
+FROM CTE_validation
+WHERE
+    /* Missing or empty AssessmentRegimeId is handled by ARZ_02_A. */
+    [AssessmentRegimeId] IS NOT NULL
+    /* Missing or invalid components are handled by their respective
+       attribute-level QC rules. */
+    AND [ExpectedAssessmentRegimeId] IS NOT NULL
+    /* Return only actual naming-convention failures. */
+    AND [IsValidAssessmentRegimeId] = 0;
+GO</t>
+  </si>
+  <si>
+    <t>[ARZ_02_B_TEST] correction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USE [Airquality_R3]
+GO
+/****** Object:  View [qc].[ARZ_02_B]    Script Date: 21/09/2026 13:28:52 ******/
+SET ANSI_NULLS ON
+GO
+SET QUOTED_IDENTIFIER ON
+GO
+CREATE   VIEW [qc].[ARZ_02_B]
+AS
+-- QC rule code: ARZ_02_B
+-- QC rule name: Naming convention validation - [AssessmentRegimeId]
+--
+-- Returns AssessmentRegimeZone records where AssessmentRegimeId does not
+-- follow the recommended assessment regime identifier convention:
+--
+--   ARE_{ZoneId}_{PollutantId}_{ObjectiveType}_{ProtectionTarget}_
+--   {ReportingMetric}_{ClassificationYear}[_{Index}]
+--
+-- Assumptions:
+--   - Components are separated by underscore characters.
+--   - PollutantId is represented using exactly four digits.
+--   - ClassificationYear is represented using exactly four digits (YYYY).
+--   - Index is optional. When reported, it is separated by an underscore
+--     and has a maximum length of one character.
+--
+-- ZoneId may contain underscore characters. Therefore, ZoneId is not parsed
+-- from AssessmentRegimeId. The expected identifier is instead built from
+-- the attribute values reported in the same record.
+--
+-- Related attribute mappings:
+--   ARZ_03 = ZoneId
+--   ARZ_09 = PollutantId
+--   ARZ_10 = ProtectionTarget
+--   ARZ_11 = ObjectiveType
+--   ARZ_12 = ReportingMetric
+--   ARZ_18 = ClassificationYear
+--
+-- Mandatory-value validation for AssessmentRegimeId is also covered by
+-- QC rule ARZ_02_A.
+WITH CTE_source AS
+(
+    SELECT
+        [CountryCode] COLLATE Latin1_General_CI_AS AS [CountryCode],
+        [AssessmentRegimeId] COLLATE Latin1_General_CI_AS
+            AS [AssessmentRegimeIdRaw],
+        [ZoneId] COLLATE Latin1_General_CI_AS
+            AS [ZoneId],
+        [PollutantId] AS [PollutantId],
+        CONVERT(NVARCHAR(100), [ObjectiveType])
+            COLLATE Latin1_General_CI_AS AS [ObjectiveType],
+        CONVERT(NVARCHAR(100), [ProtectionTarget])
+            COLLATE Latin1_General_CI_AS AS [ProtectionTarget],
+        CONVERT(NVARCHAR(100), [ReportingMetric])
+            COLLATE Latin1_General_CI_AS AS [ReportingMetric],
+        [ClassificationYear] AS [ClassificationYear],
+        NULLIF
+        (
+            LTRIM(RTRIM([AssessmentRegimeId])) COLLATE Latin1_General_CI_AS,
+            N''
+        ) COLLATE Latin1_General_CI_AS AS [AssessmentRegimeId],
+        NULLIF
+        (
+            LTRIM(RTRIM([ZoneId])) COLLATE Latin1_General_CI_AS,
+            N''
+        ) COLLATE Latin1_General_CI_AS AS [ZoneIdNormalized],
+        NULLIF
+        (
+            LTRIM(RTRIM(CONVERT(NVARCHAR(100), [ObjectiveType])))
+                COLLATE Latin1_General_CI_AS,
+            N''
+        ) COLLATE Latin1_General_CI_AS AS [ObjectiveTypeNormalized],
+        NULLIF
+        (
+            LTRIM(RTRIM(CONVERT(NVARCHAR(100), [ProtectionTarget])))
+                COLLATE Latin1_General_CI_AS,
+            N''
+        ) COLLATE Latin1_General_CI_AS AS [ProtectionTargetNormalized],
+        NULLIF
+        (
+            LTRIM(RTRIM(CONVERT(NVARCHAR(100), [ReportingMetric])))
+                COLLATE Latin1_General_CI_AS,
+            N''
+        ) COLLATE Latin1_General_CI_AS AS [ReportingMetricNormalized],
+        TRY_CONVERT(INT, [PollutantId]) AS [PollutantIdNumeric],
+        TRY_CONVERT(INT, [ClassificationYear]) AS [ClassificationYearNumeric]
+    FROM [reporting].[AssessmentRegimeZone]
+),
+CTE_expected_identifier AS
+(
+    SELECT
+        s.*,
+        CASE
+            WHEN s.[ZoneIdNormalized] IS NOT NULL
+             AND s.[PollutantIdNumeric] BETWEEN 0 AND 9999
+             AND s.[ObjectiveTypeNormalized] IS NOT NULL
+             AND s.[ProtectionTargetNormalized] IS NOT NULL
+             AND s.[ReportingMetricNormalized] IS NOT NULL
+             AND s.[ClassificationYearNumeric] BETWEEN 1000 AND 9999
+            THEN
+                CONCAT
+                (
+                    N'ARE_' COLLATE Latin1_General_CI_AS,
+                    s.[ZoneIdNormalized] COLLATE Latin1_General_CI_AS,
+                    N'_' COLLATE Latin1_General_CI_AS,
+                    RIGHT
+                    (
+                        N'0000' + CONVERT(NVARCHAR(4), s.[PollutantIdNumeric]),
+                        4
+                    ) COLLATE Latin1_General_CI_AS,
+                    N'_' COLLATE Latin1_General_CI_AS,
+                    s.[ObjectiveTypeNormalized] COLLATE Latin1_General_CI_AS,
+                    N'_' COLLATE Latin1_General_CI_AS,
+                    s.[ProtectionTargetNormalized] COLLATE Latin1_General_CI_AS,
+                    N'_' COLLATE Latin1_General_CI_AS,
+                    s.[ReportingMetricNormalized] COLLATE Latin1_General_CI_AS,
+                    N'_' COLLATE Latin1_General_CI_AS,
+                    CONVERT(NVARCHAR(4), s.[ClassificationYearNumeric])
+                        COLLATE Latin1_General_CI_AS
+                ) COLLATE Latin1_General_CI_AS
+            ELSE NULL
+        END AS [ExpectedAssessmentRegimeId]
+    FROM CTE_source AS s
+),
+CTE_validation AS
+(
+    SELECT
+        e.*,
+        CASE
+            -- The identifier exactly matches the recommended base structure.
+            WHEN e.[AssessmentRegimeId] COLLATE Latin1_General_CI_AS
+                 = e.[ExpectedAssessmentRegimeId] COLLATE Latin1_General_CI_AS
+                THEN 1
+            -- The identifier matches the base structure followed by:
+            --   _{Index}
+            -- where Index contains exactly one character.
+            WHEN LEN(e.[AssessmentRegimeId] COLLATE Latin1_General_CI_AS)
+                 = LEN(e.[ExpectedAssessmentRegimeId] COLLATE Latin1_General_CI_AS) + 2
+             AND LEFT
+                 (
+                     e.[AssessmentRegimeId] COLLATE Latin1_General_CI_AS,
+                     LEN(e.[ExpectedAssessmentRegimeId] COLLATE Latin1_General_CI_AS)
+                 ) COLLATE Latin1_General_CI_AS
+                 = e.[ExpectedAssessmentRegimeId] COLLATE Latin1_General_CI_AS
+             AND SUBSTRING
+                 (
+                     e.[AssessmentRegimeId] COLLATE Latin1_General_CI_AS,
+                     LEN(e.[ExpectedAssessmentRegimeId] COLLATE Latin1_General_CI_AS) + 1,
+                     1
+                 ) COLLATE Latin1_General_CI_AS
+                 = N'_' COLLATE Latin1_General_CI_AS
+                THEN 1
+            ELSE 0
+        END AS [IsValidAssessmentRegimeId]
+    FROM CTE_expected_identifier AS e
+)
+SELECT
+    [CountryCode],
+    [AssessmentRegimeIdRaw] AS [AssessmentRegimeId],
+    [ZoneId],
+    [PollutantId],
+    [ObjectiveType],
+    [ProtectionTarget],
+    [ReportingMetric],
+    [ClassificationYear],
+    [ExpectedAssessmentRegimeId],
+    CASE
+        WHEN [AssessmentRegimeId] IS NULL
+            THEN 'MISSING_OR_EMPTY_ASSESSMENTREGIMEID'
+        WHEN [ExpectedAssessmentRegimeId] IS NULL
+            THEN 'MISSING_OR_INVALID_IDENTIFIER_COMPONENT'
+        WHEN [IsValidAssessmentRegimeId] = 0
+            THEN 'INVALID_ASSESSMENTREGIMEID_NAMING_CONVENTION'
+        ELSE 'UNKNOWN'
+    END AS [QC_FailureReason]
+FROM CTE_validation
+WHERE
+    [AssessmentRegimeId] IS NULL
+    OR [ExpectedAssessmentRegimeId] IS NULL
+    OR [IsValidAssessmentRegimeId] = 0;
+GO
+</t>
+  </si>
+  <si>
+    <t>[ARZ_02_B] ANTIGUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USE [Airquality_R3]
+GO
+/****** Object:  View [qctesting].[ARZ_02_B_TEST]    Script Date: 21/09/2026 13:56:53 ******/
+SET ANSI_NULLS ON
+GO
+SET QUOTED_IDENTIFIER ON
+GO
+CREATE   VIEW [qctesting].[ARZ_02_B_TEST]
+AS
+-- QC rule code: ARZ_02_B
+-- QC rule name: Naming convention validation - [AssessmentRegimeId]
+--
+-- Testing version of qc.ARZ_02_B.
+--
+-- Test data source:
+--   qctesting.AssessmentRegimeZone
+--
+-- Recommended identifier convention:
+--
+--   ARE_{ZoneId}_{PollutantId}_{ObjectiveType}_{ProtectionTarget}_
+--   {ReportingMetric}_{ClassificationYear}[_{Index}]
+--
+-- ZoneId may contain underscore characters. The expected identifier is built
+-- from the values reported in the same record instead of parsing ZoneId from
+-- AssessmentRegimeId.
+--
+-- PollutantId is formatted using four digits.
+-- ClassificationYear is formatted using four digits (YYYY).
+-- Index is optional and is limited to one character.
+WITH CTE_source AS
+(
+    SELECT
+        [CountryCode] COLLATE Latin1_General_CI_AS AS [CountryCode],
+        [AssessmentRegimeId] COLLATE Latin1_General_CI_AS
+            AS [AssessmentRegimeIdRaw],
+        [ZoneId] COLLATE Latin1_General_CI_AS
+            AS [ZoneId],
+        [PollutantId] AS [PollutantId],
+        CONVERT(NVARCHAR(100), [ObjectiveType])
+            COLLATE Latin1_General_CI_AS AS [ObjectiveType],
+        CONVERT(NVARCHAR(100), [ProtectionTarget])
+            COLLATE Latin1_General_CI_AS AS [ProtectionTarget],
+        CONVERT(NVARCHAR(100), [ReportingMetric])
+            COLLATE Latin1_General_CI_AS AS [ReportingMetric],
+        [ClassificationYear] AS [ClassificationYear],
+        NULLIF
+        (
+            LTRIM(RTRIM([AssessmentRegimeId])) COLLATE Latin1_General_CI_AS,
+            N''
+        ) COLLATE Latin1_General_CI_AS AS [AssessmentRegimeId],
+        NULLIF
+        (
+            LTRIM(RTRIM([ZoneId])) COLLATE Latin1_General_CI_AS,
+            N''
+        ) COLLATE Latin1_General_CI_AS AS [ZoneIdNormalized],
+        NULLIF
+        (
+            LTRIM(RTRIM(CONVERT(NVARCHAR(100), [ObjectiveType])))
+                COLLATE Latin1_General_CI_AS,
+            N''
+        ) COLLATE Latin1_General_CI_AS AS [ObjectiveTypeNormalized],
+        NULLIF
+        (
+            LTRIM(RTRIM(CONVERT(NVARCHAR(100), [ProtectionTarget])))
+                COLLATE Latin1_General_CI_AS,
+            N''
+        ) COLLATE Latin1_General_CI_AS AS [ProtectionTargetNormalized],
+        NULLIF
+        (
+            LTRIM(RTRIM(CONVERT(NVARCHAR(100), [ReportingMetric])))
+                COLLATE Latin1_General_CI_AS,
+            N''
+        ) COLLATE Latin1_General_CI_AS AS [ReportingMetricNormalized],
+        TRY_CONVERT(INT, [PollutantId]) AS [PollutantIdNumeric],
+        TRY_CONVERT(INT, [ClassificationYear]) AS [ClassificationYearNumeric]
+    FROM [qctesting].[AssessmentRegimeZone]
+),
+CTE_expected_identifier AS
+(
+    SELECT
+        s.*,
+        CASE
+            WHEN s.[ZoneIdNormalized] IS NOT NULL
+             AND s.[PollutantIdNumeric] BETWEEN 0 AND 9999
+             AND s.[ObjectiveTypeNormalized] IS NOT NULL
+             AND s.[ProtectionTargetNormalized] IS NOT NULL
+             AND s.[ReportingMetricNormalized] IS NOT NULL
+             AND s.[ClassificationYearNumeric] BETWEEN 1000 AND 9999
+            THEN
+                CONCAT
+                (
+                    N'ARE_' COLLATE Latin1_General_CI_AS,
+                    s.[ZoneIdNormalized] COLLATE Latin1_General_CI_AS,
+                    N'_' COLLATE Latin1_General_CI_AS,
+                    RIGHT
+                    (
+                        N'0000' + CONVERT(NVARCHAR(4), s.[PollutantIdNumeric]),
+                        4
+                    ) COLLATE Latin1_General_CI_AS,
+                    N'_' COLLATE Latin1_General_CI_AS,
+                    s.[ObjectiveTypeNormalized] COLLATE Latin1_General_CI_AS,
+                    N'_' COLLATE Latin1_General_CI_AS,
+                    s.[ProtectionTargetNormalized] COLLATE Latin1_General_CI_AS,
+                    N'_' COLLATE Latin1_General_CI_AS,
+                    s.[ReportingMetricNormalized] COLLATE Latin1_General_CI_AS,
+                    N'_' COLLATE Latin1_General_CI_AS,
+                    CONVERT(NVARCHAR(4), s.[ClassificationYearNumeric])
+                        COLLATE Latin1_General_CI_AS
+                ) COLLATE Latin1_General_CI_AS
+            ELSE NULL
+        END AS [ExpectedAssessmentRegimeId]
+    FROM CTE_source AS s
+),
+CTE_validation AS
+(
+    SELECT
+        e.*,
+        CASE
+            -- The identifier exactly matches the recommended base structure.
+            WHEN e.[AssessmentRegimeId] COLLATE Latin1_General_CI_AS
+                 = e.[ExpectedAssessmentRegimeId] COLLATE Latin1_General_CI_AS
+                THEN 1
+            -- The identifier matches the base structure followed by:
+            --   _{Index}
+            -- where Index contains exactly one character.
+            WHEN LEN(e.[AssessmentRegimeId] COLLATE Latin1_General_CI_AS)
+                 = LEN(e.[ExpectedAssessmentRegimeId] COLLATE Latin1_General_CI_AS) + 2
+             AND LEFT
+                 (
+                     e.[AssessmentRegimeId] COLLATE Latin1_General_CI_AS,
+                     LEN(e.[ExpectedAssessmentRegimeId] COLLATE Latin1_General_CI_AS)
+                 ) COLLATE Latin1_General_CI_AS
+                 = e.[ExpectedAssessmentRegimeId] COLLATE Latin1_General_CI_AS
+             AND SUBSTRING
+                 (
+                     e.[AssessmentRegimeId] COLLATE Latin1_General_CI_AS,
+                     LEN(e.[ExpectedAssessmentRegimeId] COLLATE Latin1_General_CI_AS) + 1,
+                     1
+                 ) COLLATE Latin1_General_CI_AS
+                 = N'_' COLLATE Latin1_General_CI_AS
+                THEN 1
+            ELSE 0
+        END AS [IsValidAssessmentRegimeId]
+    FROM CTE_expected_identifier AS e
+)
+SELECT
+    [CountryCode],
+    [AssessmentRegimeIdRaw] AS [AssessmentRegimeId],
+    [ZoneId],
+    [PollutantId],
+    [ObjectiveType],
+    [ProtectionTarget],
+    [ReportingMetric],
+    [ClassificationYear],
+    [ExpectedAssessmentRegimeId],
+    CASE
+        WHEN [AssessmentRegimeId] IS NULL
+            THEN 'MISSING_OR_EMPTY_ASSESSMENTREGIMEID'
+        WHEN [ExpectedAssessmentRegimeId] IS NULL
+            THEN 'MISSING_OR_INVALID_IDENTIFIER_COMPONENT'
+        WHEN [IsValidAssessmentRegimeId] = 0
+            THEN 'INVALID_ASSESSMENTREGIMEID_NAMING_CONVENTION'
+        ELSE 'UNKNOWN'
+    END AS [QC_FailureReason]
+FROM CTE_validation
+WHERE
+    [AssessmentRegimeId] IS NULL
+    OR [ExpectedAssessmentRegimeId] IS NULL
+    OR [IsValidAssessmentRegimeId] = 0;
+GO
+</t>
+  </si>
+  <si>
+    <t>[ARZ_02_B_TEST] ANTIGUA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="42">
+  <fonts count="43" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3256,11 +4147,6 @@
       <name val="Verdana"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Verdana"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Verdana"/>
@@ -3271,35 +4157,45 @@
       <name val="Verdana"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Verdana"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Verdana"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Verdana"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF333333"/>
       <name val="Verdana"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF333333"/>
-      <name val="Verdana"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF333333"/>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color rgb="FF222222"/>
       <name val="Verdana"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3443,8 +4339,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -3619,166 +4521,171 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBBBBBB"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF45B0E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF45B0E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="4"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="25" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="36" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="37" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="38" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="38" fillId="25" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="25" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="36" fillId="25" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="39" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="41" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
-    <cellStyle name="Incorrecto" xfId="4" builtinId="27"/>
+    <cellStyle name="Bad" xfId="4" builtinId="27"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -3880,46 +4787,6 @@
           <bgColor rgb="FFFFFFDD"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Verdana"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Verdana"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Verdana"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Verdana"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Verdana"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Verdana"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Verdana"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Verdana"/>
-      </font>
     </dxf>
     <dxf>
       <fill>
@@ -4042,6 +4909,47 @@
         <scheme val="minor"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <name val="Verdana"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Verdana"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Verdana"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Verdana"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Verdana"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+        <name val="Verdana"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Verdana"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Verdana"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4097,8 +5005,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Table911" displayName="Table911" ref="A17:B18">
-  <autoFilter ref="A17:B18" xr:uid="{00000000-0009-0000-0100-00000A000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Table911" displayName="Table911" ref="A17:B19">
+  <autoFilter ref="A17:B19" xr:uid="{00000000-0009-0000-0100-00000A000000}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="OLD name"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="NEW name"/>
@@ -4111,7 +5019,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="Table11" displayName="Table11" ref="A2:G14">
   <autoFilter ref="A2:G14" xr:uid="{00000000-0009-0000-0100-00000B000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="QC rule" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="QC rule" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="Description"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="Task"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0A00-000004000000}" name="Task 2"/>
@@ -4124,16 +5032,16 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="Tabla1" displayName="Tabla1" ref="A3:G36" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="Tabla1" displayName="Tabla1" ref="A3:G36" dataDxfId="26">
   <autoFilter ref="A3:G36" xr:uid="{00000000-0009-0000-0100-00000C000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="QC rule" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="Description" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="Status" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="Github" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0B00-000005000000}" name="Tested" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0B00-000006000000}" name="Comments" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{ADE97F25-BC05-494F-BCB2-1A8A498F9B28}" name="Assigne" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="QC rule" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="Description" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="Status" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="Github" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0B00-000005000000}" name="Tested" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0B00-000006000000}" name="Comments" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{ADE97F25-BC05-494F-BCB2-1A8A498F9B28}" name="Assigne" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4181,15 +5089,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table13" displayName="Table13" ref="A2:I22">
   <autoFilter ref="A2:I22" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Table" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="QC rule" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Description" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Task" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Task2" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Status" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Github" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Tested" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Comments" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Table" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="QC rule" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Description" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Task" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Task2" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Status" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Github" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Tested" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Comments" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4199,8 +5107,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table46" displayName="Table46" ref="A24:B28">
   <autoFilter ref="A24:B28" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="OLD name" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="NEW name" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="OLD name" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="NEW name" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4241,7 +5149,7 @@
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="QC rule"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Description"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Task" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Task" dataDxfId="7"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Status"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="Github"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Tested"/>
@@ -4591,7 +5499,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I51"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -4603,7 +5511,7 @@
     <col min="9" max="9" width="71.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4611,7 +5519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -4640,7 +5548,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16.5">
+    <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -4663,7 +5571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -4676,7 +5584,7 @@
       <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="79" t="s">
+      <c r="E4" s="78" t="s">
         <v>19</v>
       </c>
       <c r="F4" t="s">
@@ -4689,7 +5597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -4702,7 +5610,7 @@
       <c r="D5" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="79" t="s">
+      <c r="E5" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F5" t="s">
@@ -4715,7 +5623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -4728,7 +5636,7 @@
       <c r="D6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="79" t="s">
+      <c r="E6" s="78" t="s">
         <v>29</v>
       </c>
       <c r="F6" t="s">
@@ -4741,7 +5649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1">
+    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -4764,7 +5672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1">
+    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -4787,7 +5695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1">
+    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -4810,7 +5718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -4836,7 +5744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -4862,7 +5770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -4888,7 +5796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -4914,7 +5822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -4940,7 +5848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -4966,7 +5874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -4992,7 +5900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -5021,7 +5929,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -5050,7 +5958,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -5076,7 +5984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -5102,7 +6010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>11</v>
       </c>
@@ -5126,7 +6034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1">
+    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>11</v>
       </c>
@@ -5149,7 +6057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>11</v>
       </c>
@@ -5173,7 +6081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>11</v>
       </c>
@@ -5197,7 +6105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>11</v>
       </c>
@@ -5212,7 +6120,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.75">
+    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>11</v>
       </c>
@@ -5227,7 +6135,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>11</v>
       </c>
@@ -5242,7 +6150,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="10" customFormat="1">
+    <row r="28" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>11</v>
       </c>
@@ -5256,7 +6164,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="10" customFormat="1">
+    <row r="29" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>11</v>
       </c>
@@ -5270,7 +6178,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="10" customFormat="1">
+    <row r="30" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>11</v>
       </c>
@@ -5284,7 +6192,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="10" customFormat="1">
+    <row r="31" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>11</v>
       </c>
@@ -5298,7 +6206,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="10" customFormat="1">
+    <row r="32" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>11</v>
       </c>
@@ -5312,7 +6220,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:5" s="10" customFormat="1">
+    <row r="33" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>11</v>
       </c>
@@ -5326,7 +6234,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>124</v>
       </c>
@@ -5334,7 +6242,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>126</v>
       </c>
@@ -5342,7 +6250,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>128</v>
       </c>
@@ -5350,7 +6258,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>130</v>
       </c>
@@ -5358,7 +6266,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>131</v>
       </c>
@@ -5366,7 +6274,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>132</v>
       </c>
@@ -5374,19 +6282,19 @@
         <v>133</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>135</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="12"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>136</v>
       </c>
@@ -5394,7 +6302,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>138</v>
       </c>
@@ -5402,15 +6310,15 @@
         <v>139</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="13"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
         <v>63</v>
       </c>
@@ -5418,7 +6326,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="15" t="s">
         <v>108</v>
       </c>
@@ -5429,7 +6337,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
         <v>95</v>
       </c>
@@ -5440,7 +6348,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="15" t="s">
         <v>98</v>
       </c>
@@ -5491,7 +6399,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I49"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.140625" customWidth="1"/>
@@ -5503,7 +6411,7 @@
     <col min="9" max="9" width="185.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5511,7 +6419,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -5540,7 +6448,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15" customHeight="1">
+    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>145</v>
       </c>
@@ -5553,7 +6461,7 @@
       <c r="D3" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E3" s="80" t="s">
+      <c r="E3" s="79" t="s">
         <v>149</v>
       </c>
       <c r="F3" t="s">
@@ -5569,7 +6477,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>145</v>
       </c>
@@ -5595,7 +6503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>145</v>
       </c>
@@ -5608,7 +6516,7 @@
       <c r="D5" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E5" s="79" t="s">
+      <c r="E5" s="78" t="s">
         <v>160</v>
       </c>
       <c r="F5" t="s">
@@ -5621,7 +6529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="20" customFormat="1">
+    <row r="6" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
         <v>145</v>
       </c>
@@ -5644,7 +6552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="22" customFormat="1">
+    <row r="7" spans="1:9" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>145</v>
       </c>
@@ -5671,7 +6579,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>145</v>
       </c>
@@ -5697,7 +6605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>145</v>
       </c>
@@ -5710,7 +6618,7 @@
       <c r="D9" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="E9" s="79" t="s">
+      <c r="E9" s="78" t="s">
         <v>177</v>
       </c>
       <c r="F9" t="s">
@@ -5723,7 +6631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>145</v>
       </c>
@@ -5736,7 +6644,7 @@
       <c r="D10" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E10" s="79" t="s">
+      <c r="E10" s="78" t="s">
         <v>181</v>
       </c>
       <c r="F10" s="12" t="s">
@@ -5752,7 +6660,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>145</v>
       </c>
@@ -5781,7 +6689,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>145</v>
       </c>
@@ -5808,7 +6716,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>145</v>
       </c>
@@ -5821,7 +6729,7 @@
       <c r="D13" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="E13" s="79" t="s">
+      <c r="E13" s="78" t="s">
         <v>195</v>
       </c>
       <c r="F13" s="12" t="s">
@@ -5837,7 +6745,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>145</v>
       </c>
@@ -5862,7 +6770,7 @@
       </c>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:9" ht="30">
+    <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>145</v>
       </c>
@@ -5881,7 +6789,7 @@
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
     </row>
-    <row r="16" spans="1:9" ht="30">
+    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>145</v>
       </c>
@@ -5900,7 +6808,7 @@
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="30" t="s">
         <v>145</v>
       </c>
@@ -5919,7 +6827,7 @@
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
     </row>
-    <row r="18" spans="1:9" ht="18" customHeight="1">
+    <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="31" t="s">
         <v>145</v>
       </c>
@@ -5940,7 +6848,7 @@
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
     </row>
-    <row r="19" spans="1:9" ht="30">
+    <row r="19" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
         <v>145</v>
       </c>
@@ -5959,7 +6867,7 @@
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
     </row>
-    <row r="20" spans="1:9" ht="30">
+    <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="s">
         <v>145</v>
       </c>
@@ -5978,7 +6886,7 @@
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
     </row>
-    <row r="21" spans="1:9" ht="13.5" customHeight="1">
+    <row r="21" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>145</v>
       </c>
@@ -5999,7 +6907,7 @@
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
     </row>
-    <row r="22" spans="1:9" ht="30">
+    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>145</v>
       </c>
@@ -6018,7 +6926,7 @@
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>124</v>
       </c>
@@ -6026,7 +6934,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>224</v>
       </c>
@@ -6034,7 +6942,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>226</v>
       </c>
@@ -6042,7 +6950,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>132</v>
       </c>
@@ -6050,7 +6958,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>229</v>
       </c>
@@ -6058,52 +6966,52 @@
         <v>230</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="18"/>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="36"/>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="36"/>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="37"/>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="38"/>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="36"/>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="36"/>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="37"/>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="38"/>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="36"/>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="36"/>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="37"/>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="38"/>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="36"/>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="36"/>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="37"/>
     </row>
   </sheetData>
@@ -6144,7 +7052,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I46"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -6155,7 +7063,7 @@
     <col min="9" max="9" width="109.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6163,7 +7071,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -6192,7 +7100,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16.5">
+    <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>233</v>
       </c>
@@ -6205,7 +7113,7 @@
       <c r="D3" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="E3" s="79" t="s">
+      <c r="E3" s="78" t="s">
         <v>237</v>
       </c>
       <c r="F3" s="6" t="s">
@@ -6221,7 +7129,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16.5">
+    <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>233</v>
       </c>
@@ -6234,7 +7142,7 @@
       <c r="D4" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="E4" s="79" t="s">
+      <c r="E4" s="78" t="s">
         <v>243</v>
       </c>
       <c r="F4" s="6" t="s">
@@ -6248,7 +7156,7 @@
       </c>
       <c r="I4" s="6"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>233</v>
       </c>
@@ -6261,7 +7169,7 @@
       <c r="D5" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="E5" s="79" t="s">
+      <c r="E5" s="78" t="s">
         <v>247</v>
       </c>
       <c r="F5" s="6" t="s">
@@ -6275,7 +7183,7 @@
       </c>
       <c r="I5" s="6"/>
     </row>
-    <row r="6" spans="1:9" ht="90.75">
+    <row r="6" spans="1:9" ht="90.75" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>233</v>
       </c>
@@ -6298,7 +7206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16.5">
+    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>233</v>
       </c>
@@ -6325,7 +7233,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16.5">
+    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>233</v>
       </c>
@@ -6352,7 +7260,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="16.5">
+    <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>233</v>
       </c>
@@ -6365,7 +7273,7 @@
       <c r="D9" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="E9" s="79" t="s">
+      <c r="E9" s="78" t="s">
         <v>263</v>
       </c>
       <c r="F9" t="s">
@@ -6381,7 +7289,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>233</v>
       </c>
@@ -6400,7 +7308,7 @@
       <c r="H10" s="8"/>
       <c r="I10" s="27"/>
     </row>
-    <row r="11" spans="1:9" ht="30">
+    <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>233</v>
       </c>
@@ -6419,7 +7327,7 @@
       <c r="H11" s="8"/>
       <c r="I11" s="27"/>
     </row>
-    <row r="12" spans="1:9" ht="30">
+    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>233</v>
       </c>
@@ -6438,7 +7346,7 @@
       <c r="H12" s="8"/>
       <c r="I12" s="27"/>
     </row>
-    <row r="13" spans="1:9" ht="45">
+    <row r="13" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>233</v>
       </c>
@@ -6457,7 +7365,7 @@
       <c r="H13" s="8"/>
       <c r="I13" s="27"/>
     </row>
-    <row r="14" spans="1:9" ht="30">
+    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>233</v>
       </c>
@@ -6476,12 +7384,12 @@
       <c r="H14" s="8"/>
       <c r="I14" s="27"/>
     </row>
-    <row r="15" spans="1:9" ht="16.5">
+    <row r="15" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="C15" s="1"/>
       <c r="D15" s="5"/>
       <c r="E15" s="42"/>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" ht="16.5">
+    <row r="16" spans="1:9" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="43" t="s">
         <v>233</v>
       </c>
@@ -6495,7 +7403,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="46" t="s">
         <v>233</v>
       </c>
@@ -6503,7 +7411,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="18" spans="1:2" s="2" customFormat="1">
+    <row r="18" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="43" t="s">
         <v>233</v>
       </c>
@@ -6511,7 +7419,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="19" spans="1:2" s="2" customFormat="1">
+    <row r="19" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="43" t="s">
         <v>233</v>
       </c>
@@ -6519,7 +7427,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="20" spans="1:2" s="2" customFormat="1">
+    <row r="20" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="43" t="s">
         <v>233</v>
       </c>
@@ -6527,7 +7435,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="21" spans="1:2" s="2" customFormat="1">
+    <row r="21" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="43" t="s">
         <v>233</v>
       </c>
@@ -6535,7 +7443,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="22" spans="1:2" s="2" customFormat="1">
+    <row r="22" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="43" t="s">
         <v>233</v>
       </c>
@@ -6543,7 +7451,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="23" spans="1:2" s="2" customFormat="1">
+    <row r="23" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="43" t="s">
         <v>233</v>
       </c>
@@ -6551,7 +7459,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="24" spans="1:2" s="47" customFormat="1">
+    <row r="24" spans="1:2" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="48" t="s">
         <v>233</v>
       </c>
@@ -6559,7 +7467,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="25" spans="1:2" s="2" customFormat="1">
+    <row r="25" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="43" t="s">
         <v>233</v>
       </c>
@@ -6567,7 +7475,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="26" spans="1:2" s="2" customFormat="1">
+    <row r="26" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="43" t="s">
         <v>233</v>
       </c>
@@ -6575,7 +7483,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="27" spans="1:2" s="2" customFormat="1">
+    <row r="27" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="43" t="s">
         <v>233</v>
       </c>
@@ -6583,13 +7491,13 @@
         <v>286</v>
       </c>
     </row>
-    <row r="28" spans="1:2" s="2" customFormat="1">
+    <row r="28" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="43"/>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="46"/>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>124</v>
       </c>
@@ -6597,7 +7505,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>226</v>
       </c>
@@ -6605,7 +7513,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>287</v>
       </c>
@@ -6613,7 +7521,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>132</v>
       </c>
@@ -6621,42 +7529,42 @@
         <v>228</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>296</v>
       </c>
@@ -6690,7 +7598,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:CW37"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.5703125" customWidth="1"/>
     <col min="2" max="2" width="70.140625" customWidth="1"/>
@@ -6701,15 +7609,15 @@
     <col min="7" max="7" width="57.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
     </row>
-    <row r="3" spans="1:7" s="50" customFormat="1" ht="18.75">
+    <row r="3" spans="1:7" s="50" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="50" t="s">
         <v>3</v>
       </c>
@@ -6732,7 +7640,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.5">
+    <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>298</v>
       </c>
@@ -6755,7 +7663,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.5">
+    <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>302</v>
       </c>
@@ -6778,7 +7686,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>304</v>
       </c>
@@ -6798,7 +7706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>308</v>
       </c>
@@ -6818,7 +7726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
         <v>311</v>
       </c>
@@ -6839,7 +7747,7 @@
       </c>
       <c r="G9" s="53"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>314</v>
       </c>
@@ -6862,7 +7770,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="52" t="s">
         <v>318</v>
       </c>
@@ -6883,7 +7791,7 @@
       </c>
       <c r="G11" s="53"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="52" t="s">
         <v>321</v>
       </c>
@@ -6904,7 +7812,7 @@
       </c>
       <c r="G12" s="53"/>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>324</v>
       </c>
@@ -6924,7 +7832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="52" t="s">
         <v>327</v>
       </c>
@@ -6945,7 +7853,7 @@
       </c>
       <c r="G14" s="53"/>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>298</v>
       </c>
@@ -6965,7 +7873,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>302</v>
       </c>
@@ -6985,7 +7893,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="17" spans="1:101">
+    <row r="17" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>333</v>
       </c>
@@ -7005,7 +7913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:101">
+    <row r="18" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A18" s="56" t="s">
         <v>336</v>
       </c>
@@ -7026,7 +7934,7 @@
       </c>
       <c r="G18" s="53"/>
     </row>
-    <row r="19" spans="1:101">
+    <row r="19" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A19" s="56" t="s">
         <v>339</v>
       </c>
@@ -7047,7 +7955,7 @@
       </c>
       <c r="G19" s="53"/>
     </row>
-    <row r="20" spans="1:101">
+    <row r="20" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A20" s="56" t="s">
         <v>342</v>
       </c>
@@ -7068,7 +7976,7 @@
       </c>
       <c r="G20" s="53"/>
     </row>
-    <row r="21" spans="1:101" s="2" customFormat="1">
+    <row r="21" spans="1:101" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>345</v>
       </c>
@@ -7183,7 +8091,7 @@
       <c r="CV21"/>
       <c r="CW21"/>
     </row>
-    <row r="22" spans="1:101" s="2" customFormat="1">
+    <row r="22" spans="1:101" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="58" t="s">
         <v>348</v>
       </c>
@@ -7298,7 +8206,7 @@
       <c r="CV22"/>
       <c r="CW22"/>
     </row>
-    <row r="23" spans="1:101" s="2" customFormat="1">
+    <row r="23" spans="1:101" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>351</v>
       </c>
@@ -7413,7 +8321,7 @@
       <c r="CV23"/>
       <c r="CW23"/>
     </row>
-    <row r="24" spans="1:101" s="2" customFormat="1">
+    <row r="24" spans="1:101" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>354</v>
       </c>
@@ -7528,7 +8436,7 @@
       <c r="CV24"/>
       <c r="CW24"/>
     </row>
-    <row r="25" spans="1:101" s="2" customFormat="1">
+    <row r="25" spans="1:101" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>356</v>
       </c>
@@ -7643,7 +8551,7 @@
       <c r="CV25"/>
       <c r="CW25"/>
     </row>
-    <row r="26" spans="1:101" s="2" customFormat="1">
+    <row r="26" spans="1:101" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>359</v>
       </c>
@@ -7758,7 +8666,7 @@
       <c r="CV26"/>
       <c r="CW26"/>
     </row>
-    <row r="27" spans="1:101">
+    <row r="27" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>362</v>
       </c>
@@ -7778,7 +8686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:101">
+    <row r="28" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>365</v>
       </c>
@@ -7798,7 +8706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:101">
+    <row r="29" spans="1:101" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>368</v>
       </c>
@@ -7818,13 +8726,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="53"/>
       <c r="C34" s="5"/>
       <c r="E34" s="51"/>
       <c r="G34" s="53"/>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>124</v>
       </c>
@@ -7832,7 +8740,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="60" t="s">
         <v>371</v>
       </c>
@@ -7878,8 +8786,8 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="15"/>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -7892,7 +8800,7 @@
     <col min="9" max="9" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7900,7 +8808,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -7929,7 +8837,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>374</v>
       </c>
@@ -7949,7 +8857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>374</v>
       </c>
@@ -7969,7 +8877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>374</v>
       </c>
@@ -7988,8 +8896,11 @@
       <c r="H5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="I5" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>374</v>
       </c>
@@ -8012,7 +8923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>374</v>
       </c>
@@ -8035,7 +8946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>374</v>
       </c>
@@ -8052,7 +8963,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>374</v>
       </c>
@@ -8069,7 +8980,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>374</v>
       </c>
@@ -8086,7 +8997,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>374</v>
       </c>
@@ -8103,7 +9014,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>401</v>
       </c>
@@ -8111,7 +9022,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>124</v>
       </c>
@@ -8119,12 +9030,28 @@
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="60" t="s">
         <v>371</v>
       </c>
       <c r="B18" t="s">
         <v>372</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="120.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="110" t="s">
+        <v>575</v>
+      </c>
+      <c r="B19" s="110" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="B20" s="111" t="s">
+        <v>576</v>
       </c>
     </row>
   </sheetData>
@@ -8143,7 +9070,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.85546875" customWidth="1"/>
     <col min="2" max="2" width="27.28515625" customWidth="1"/>
@@ -8151,7 +9078,7 @@
     <col min="7" max="7" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>403</v>
       </c>
@@ -8159,7 +9086,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="61" t="s">
         <v>3</v>
       </c>
@@ -8182,7 +9109,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>405</v>
       </c>
@@ -8198,7 +9125,7 @@
       </c>
       <c r="F3" s="14"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>409</v>
       </c>
@@ -8212,7 +9139,7 @@
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>412</v>
       </c>
@@ -8225,7 +9152,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>414</v>
       </c>
@@ -8237,7 +9164,7 @@
       </c>
       <c r="F6" s="15"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>415</v>
       </c>
@@ -8247,7 +9174,7 @@
       <c r="E7" s="14"/>
       <c r="F7" s="14"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>416</v>
       </c>
@@ -8259,7 +9186,7 @@
       </c>
       <c r="F8" s="15"/>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>417</v>
       </c>
@@ -8271,7 +9198,7 @@
       </c>
       <c r="F9" s="14"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>418</v>
       </c>
@@ -8283,7 +9210,7 @@
       </c>
       <c r="F10" s="15"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>419</v>
       </c>
@@ -8295,22 +9222,22 @@
       </c>
       <c r="F11" s="14"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>423</v>
       </c>
@@ -8321,7 +9248,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="409.5">
+    <row r="18" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A18" s="40" t="s">
         <v>426</v>
       </c>
@@ -8357,11 +9284,11 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G85"/>
-  <sheetFormatPr defaultRowHeight="21"/>
+  <dimension ref="A1:G86"/>
+  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="74.140625" customWidth="1"/>
-    <col min="2" max="2" width="50.42578125" customWidth="1"/>
+    <col min="2" max="2" width="86.5703125" style="97" customWidth="1"/>
     <col min="3" max="3" width="30.28515625" style="63" customWidth="1"/>
     <col min="4" max="4" width="19.140625" customWidth="1"/>
     <col min="5" max="5" width="24.28515625" customWidth="1"/>
@@ -8369,893 +9296,971 @@
     <col min="7" max="7" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="64" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="65" customFormat="1" ht="24">
-      <c r="A3" s="66" t="s">
+    <row r="3" spans="1:7" s="64" customFormat="1" ht="24" x14ac:dyDescent="0.4">
+      <c r="A3" s="65" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="66" t="s">
+      <c r="C3" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="66" t="s">
+      <c r="D3" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="66" t="s">
+      <c r="E3" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="66" t="s">
+      <c r="F3" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="65" t="s">
+      <c r="G3" s="64" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="19.5">
-      <c r="A4" s="86" t="s">
+    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="85" t="s">
         <v>431</v>
       </c>
-      <c r="B4" s="86" t="s">
+      <c r="B4" s="85" t="s">
         <v>432</v>
       </c>
-      <c r="C4" s="87" t="s">
-        <v>433</v>
-      </c>
-      <c r="D4" s="86" t="s">
+      <c r="C4" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D4" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="E4" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="85"/>
+      <c r="G4" s="86" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="85" t="s">
+        <v>436</v>
+      </c>
+      <c r="B5" s="98" t="s">
+        <v>564</v>
+      </c>
+      <c r="C5" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D5" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="E5" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="101" t="s">
+        <v>572</v>
+      </c>
+      <c r="G5" s="86" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="85" t="s">
+        <v>440</v>
+      </c>
+      <c r="B6" s="98" t="s">
+        <v>565</v>
+      </c>
+      <c r="C6" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D6" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="E6" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="85"/>
+      <c r="G6" s="86" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="85" t="s">
+        <v>441</v>
+      </c>
+      <c r="B7" s="98" t="s">
+        <v>566</v>
+      </c>
+      <c r="C7" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D7" s="85" t="s">
         <v>434</v>
       </c>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="88" t="s">
+      <c r="E7" s="85" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="85"/>
+      <c r="G7" s="86" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="85" t="s">
+        <v>442</v>
+      </c>
+      <c r="B8" s="98" t="s">
+        <v>567</v>
+      </c>
+      <c r="C8" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D8" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="E8" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="85"/>
+      <c r="G8" s="86" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="85" t="s">
+        <v>443</v>
+      </c>
+      <c r="B9" s="98" t="s">
+        <v>568</v>
+      </c>
+      <c r="C9" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D9" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="E9" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="85"/>
+      <c r="G9" s="86" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="85" t="s">
+        <v>444</v>
+      </c>
+      <c r="B10" s="98" t="s">
+        <v>569</v>
+      </c>
+      <c r="C10" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D10" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="E10" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="85"/>
+      <c r="G10" s="86" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="85" t="s">
+        <v>445</v>
+      </c>
+      <c r="B11" s="85"/>
+      <c r="C11" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D11" s="85"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85" t="s">
+        <v>571</v>
+      </c>
+      <c r="G11" s="86" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="85" t="s">
+        <v>447</v>
+      </c>
+      <c r="B12" s="85"/>
+      <c r="C12" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D12" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="E12" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="85"/>
+      <c r="G12" s="86" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="85" t="s">
+        <v>448</v>
+      </c>
+      <c r="B13" s="87" t="s">
+        <v>449</v>
+      </c>
+      <c r="C13" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D13" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="E13" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" s="85"/>
+      <c r="G13" s="86" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75">
-      <c r="A5" s="86" t="s">
-        <v>436</v>
-      </c>
-      <c r="B5" s="103" t="s">
+    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="85" t="s">
+        <v>450</v>
+      </c>
+      <c r="B14" s="85" t="s">
+        <v>451</v>
+      </c>
+      <c r="C14" s="84" t="s">
         <v>437</v>
       </c>
-      <c r="C5" s="85" t="s">
+      <c r="D14" s="85" t="s">
         <v>438</v>
       </c>
-      <c r="D5" s="86" t="s">
+      <c r="E14" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="85"/>
+      <c r="G14" s="86" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="85" t="s">
+        <v>452</v>
+      </c>
+      <c r="B15" s="85" t="s">
+        <v>453</v>
+      </c>
+      <c r="C15" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D15" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="E15" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="85"/>
+      <c r="G15" s="86" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="85" t="s">
+        <v>454</v>
+      </c>
+      <c r="B16" s="85"/>
+      <c r="C16" s="100" t="s">
+        <v>446</v>
+      </c>
+      <c r="D16" s="85"/>
+      <c r="E16" s="85"/>
+      <c r="F16" s="85"/>
+      <c r="G16" s="86" t="s">
         <v>439</v>
       </c>
-      <c r="E5" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" s="86"/>
-      <c r="G5" s="88" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.75">
-      <c r="A6" s="86" t="s">
-        <v>441</v>
-      </c>
-      <c r="B6" s="103" t="s">
-        <v>442</v>
-      </c>
-      <c r="C6" s="85" t="s">
+    </row>
+    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="85" t="s">
+        <v>455</v>
+      </c>
+      <c r="B17" s="85" t="s">
+        <v>559</v>
+      </c>
+      <c r="C17" s="100" t="s">
+        <v>446</v>
+      </c>
+      <c r="D17" s="85"/>
+      <c r="E17" s="85"/>
+      <c r="F17" s="85"/>
+      <c r="G17" s="86" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="85" t="s">
+        <v>456</v>
+      </c>
+      <c r="B18" s="87" t="s">
+        <v>457</v>
+      </c>
+      <c r="C18" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D18" s="85" t="s">
         <v>438</v>
       </c>
-      <c r="D6" s="86" t="s">
+      <c r="E18" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="85"/>
+      <c r="G18" s="86" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="85" t="s">
+        <v>458</v>
+      </c>
+      <c r="B19" s="87" t="s">
+        <v>459</v>
+      </c>
+      <c r="C19" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D19" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="E19" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="85"/>
+      <c r="G19" s="86" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="85" t="s">
+        <v>460</v>
+      </c>
+      <c r="B20" s="87" t="s">
+        <v>461</v>
+      </c>
+      <c r="C20" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D20" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="E20" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" s="85"/>
+      <c r="G20" s="86" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="85" t="s">
+        <v>462</v>
+      </c>
+      <c r="B21" s="85" t="s">
+        <v>560</v>
+      </c>
+      <c r="C21" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D21" s="85" t="s">
+        <v>434</v>
+      </c>
+      <c r="E21" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" s="85"/>
+      <c r="G21" s="86" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="85" t="s">
+        <v>463</v>
+      </c>
+      <c r="B22" s="85" t="s">
+        <v>464</v>
+      </c>
+      <c r="C22" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D22" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="E22" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" s="85"/>
+      <c r="G22" s="86" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="85" t="s">
+        <v>465</v>
+      </c>
+      <c r="B23" s="85" t="s">
+        <v>561</v>
+      </c>
+      <c r="C23" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D23" s="85" t="s">
+        <v>434</v>
+      </c>
+      <c r="E23" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" s="85"/>
+      <c r="G23" s="86" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="85" t="s">
+        <v>466</v>
+      </c>
+      <c r="B24" s="85" t="s">
+        <v>467</v>
+      </c>
+      <c r="C24" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D24" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="E24" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" s="85"/>
+      <c r="G24" s="86" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="85" t="s">
+        <v>468</v>
+      </c>
+      <c r="B25" s="85" t="s">
+        <v>469</v>
+      </c>
+      <c r="C25" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D25" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="E25" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" s="85"/>
+      <c r="G25" s="86" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="85" t="s">
+        <v>470</v>
+      </c>
+      <c r="B26" s="85" t="s">
+        <v>471</v>
+      </c>
+      <c r="C26" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D26" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="E26" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" s="85"/>
+      <c r="G26" s="86" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="85" t="s">
+        <v>472</v>
+      </c>
+      <c r="B27" s="85" t="s">
+        <v>473</v>
+      </c>
+      <c r="C27" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D27" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="E27" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" s="85"/>
+      <c r="G27" s="86" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="88" t="s">
+        <v>474</v>
+      </c>
+      <c r="B28" s="89" t="s">
+        <v>475</v>
+      </c>
+      <c r="C28" s="102" t="s">
+        <v>573</v>
+      </c>
+      <c r="D28" s="85" t="s">
+        <v>438</v>
+      </c>
+      <c r="E28" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="90"/>
+      <c r="G28" s="91" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" s="109" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="104" t="s">
+        <v>476</v>
+      </c>
+      <c r="B29" s="105" t="s">
+        <v>477</v>
+      </c>
+      <c r="C29" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D29" s="89" t="s">
+        <v>438</v>
+      </c>
+      <c r="E29" s="106" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="107"/>
+      <c r="G29" s="108" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="88" t="s">
+        <v>478</v>
+      </c>
+      <c r="B30" s="89" t="s">
+        <v>479</v>
+      </c>
+      <c r="C30" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D30" s="89" t="s">
+        <v>438</v>
+      </c>
+      <c r="E30" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" s="90"/>
+      <c r="G30" s="91" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="92" t="s">
+        <v>480</v>
+      </c>
+      <c r="B31" s="93" t="s">
+        <v>481</v>
+      </c>
+      <c r="C31" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D31" s="93" t="s">
+        <v>438</v>
+      </c>
+      <c r="E31" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" s="94"/>
+      <c r="G31" s="95" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="88" t="s">
+        <v>482</v>
+      </c>
+      <c r="B32" s="89" t="s">
+        <v>562</v>
+      </c>
+      <c r="C32" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D32" s="89" t="s">
+        <v>438</v>
+      </c>
+      <c r="E32" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" s="90"/>
+      <c r="G32" s="91" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="92" t="s">
+        <v>483</v>
+      </c>
+      <c r="B33" s="93" t="s">
+        <v>563</v>
+      </c>
+      <c r="C33" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D33" s="93" t="s">
+        <v>438</v>
+      </c>
+      <c r="E33" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" s="94" t="s">
+        <v>570</v>
+      </c>
+      <c r="G33" s="95" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="96" t="s">
+        <v>484</v>
+      </c>
+      <c r="B34" s="99" t="s">
+        <v>485</v>
+      </c>
+      <c r="C34" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D34" s="93" t="s">
+        <v>438</v>
+      </c>
+      <c r="E34" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" s="90"/>
+      <c r="G34" s="91" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="85" t="s">
+        <v>486</v>
+      </c>
+      <c r="B35" s="85"/>
+      <c r="C35" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D35" s="93" t="s">
+        <v>438</v>
+      </c>
+      <c r="E35" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" s="85"/>
+      <c r="G35" s="86" t="s">
         <v>439</v>
       </c>
-      <c r="E6" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" s="86"/>
-      <c r="G6" s="88" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.75">
-      <c r="A7" s="86" t="s">
-        <v>443</v>
-      </c>
-      <c r="B7" s="103" t="s">
-        <v>444</v>
-      </c>
-      <c r="C7" s="85" t="s">
+    </row>
+    <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="85" t="s">
+        <v>487</v>
+      </c>
+      <c r="B36" s="85"/>
+      <c r="C36" s="84" t="s">
+        <v>437</v>
+      </c>
+      <c r="D36" s="93" t="s">
         <v>438</v>
       </c>
-      <c r="D7" s="86" t="s">
+      <c r="E36" s="85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" s="85"/>
+      <c r="G36" s="86" t="s">
         <v>439</v>
       </c>
-      <c r="E7" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" s="86"/>
-      <c r="G7" s="88" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.75">
-      <c r="A8" s="86" t="s">
-        <v>445</v>
-      </c>
-      <c r="B8" s="103" t="s">
-        <v>446</v>
-      </c>
-      <c r="C8" s="85" t="s">
-        <v>438</v>
-      </c>
-      <c r="D8" s="86" t="s">
-        <v>439</v>
-      </c>
-      <c r="E8" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" s="86"/>
-      <c r="G8" s="88" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.75">
-      <c r="A9" s="86" t="s">
-        <v>447</v>
-      </c>
-      <c r="B9" s="103" t="s">
-        <v>448</v>
-      </c>
-      <c r="C9" s="85" t="s">
-        <v>438</v>
-      </c>
-      <c r="D9" s="86" t="s">
-        <v>439</v>
-      </c>
-      <c r="E9" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" s="86"/>
-      <c r="G9" s="88" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.75">
-      <c r="A10" s="86" t="s">
-        <v>449</v>
-      </c>
-      <c r="B10" s="103" t="s">
-        <v>450</v>
-      </c>
-      <c r="C10" s="85" t="s">
-        <v>438</v>
-      </c>
-      <c r="D10" s="86" t="s">
-        <v>439</v>
-      </c>
-      <c r="E10" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" s="86"/>
-      <c r="G10" s="88" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19.5">
-      <c r="A11" s="86" t="s">
-        <v>451</v>
-      </c>
-      <c r="B11" s="86"/>
-      <c r="C11" s="87" t="s">
-        <v>452</v>
-      </c>
-      <c r="D11" s="86"/>
-      <c r="E11" s="86"/>
-      <c r="F11" s="86"/>
-      <c r="G11" s="88" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="19.5">
-      <c r="A12" s="86" t="s">
-        <v>453</v>
-      </c>
-      <c r="B12" s="86"/>
-      <c r="C12" s="87" t="s">
-        <v>452</v>
-      </c>
-      <c r="D12" s="86"/>
-      <c r="E12" s="86"/>
-      <c r="F12" s="86"/>
-      <c r="G12" s="88" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15.75">
-      <c r="A13" s="86" t="s">
-        <v>454</v>
-      </c>
-      <c r="B13" s="89" t="s">
-        <v>455</v>
-      </c>
-      <c r="C13" s="85" t="s">
-        <v>438</v>
-      </c>
-      <c r="D13" s="86" t="s">
-        <v>434</v>
-      </c>
-      <c r="E13" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" s="86"/>
-      <c r="G13" s="88" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15.75">
-      <c r="A14" s="86" t="s">
-        <v>456</v>
-      </c>
-      <c r="B14" s="86" t="s">
-        <v>457</v>
-      </c>
-      <c r="C14" s="85" t="s">
-        <v>438</v>
-      </c>
-      <c r="D14" s="86" t="s">
-        <v>434</v>
-      </c>
-      <c r="E14" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" s="86"/>
-      <c r="G14" s="88" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15.75">
-      <c r="A15" s="86" t="s">
-        <v>458</v>
-      </c>
-      <c r="B15" s="86" t="s">
-        <v>459</v>
-      </c>
-      <c r="C15" s="85" t="s">
-        <v>438</v>
-      </c>
-      <c r="D15" s="86" t="s">
-        <v>434</v>
-      </c>
-      <c r="E15" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="86"/>
-      <c r="G15" s="88" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="19.5">
-      <c r="A16" s="86" t="s">
-        <v>460</v>
-      </c>
-      <c r="B16" s="86"/>
-      <c r="C16" s="87" t="s">
-        <v>452</v>
-      </c>
-      <c r="D16" s="86"/>
-      <c r="E16" s="86"/>
-      <c r="F16" s="86"/>
-      <c r="G16" s="88"/>
-    </row>
-    <row r="17" spans="1:7" ht="19.5">
-      <c r="A17" s="86" t="s">
-        <v>461</v>
-      </c>
-      <c r="B17" s="86"/>
-      <c r="C17" s="87" t="s">
-        <v>452</v>
-      </c>
-      <c r="D17" s="86"/>
-      <c r="E17" s="86"/>
-      <c r="F17" s="86"/>
-      <c r="G17" s="88"/>
-    </row>
-    <row r="18" spans="1:7" ht="15.75">
-      <c r="A18" s="86" t="s">
-        <v>462</v>
-      </c>
-      <c r="B18" s="89" t="s">
-        <v>463</v>
-      </c>
-      <c r="C18" s="85" t="s">
-        <v>438</v>
-      </c>
-      <c r="D18" s="86" t="s">
-        <v>434</v>
-      </c>
-      <c r="E18" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" s="86"/>
-      <c r="G18" s="88" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.75">
-      <c r="A19" s="86" t="s">
-        <v>464</v>
-      </c>
-      <c r="B19" s="89" t="s">
-        <v>465</v>
-      </c>
-      <c r="C19" s="85" t="s">
-        <v>438</v>
-      </c>
-      <c r="D19" s="86" t="s">
-        <v>434</v>
-      </c>
-      <c r="E19" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" s="86"/>
-      <c r="G19" s="88" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75">
-      <c r="A20" s="86" t="s">
-        <v>466</v>
-      </c>
-      <c r="B20" s="89" t="s">
-        <v>467</v>
-      </c>
-      <c r="C20" s="85" t="s">
-        <v>438</v>
-      </c>
-      <c r="D20" s="86" t="s">
-        <v>434</v>
-      </c>
-      <c r="E20" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" s="86"/>
-      <c r="G20" s="88" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="19.5">
-      <c r="A21" s="86" t="s">
-        <v>468</v>
-      </c>
-      <c r="B21" s="86"/>
-      <c r="C21" s="87" t="s">
-        <v>452</v>
-      </c>
-      <c r="D21" s="86"/>
-      <c r="E21" s="86"/>
-      <c r="F21" s="86"/>
-      <c r="G21" s="88" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="15.75">
-      <c r="A22" s="86" t="s">
-        <v>469</v>
-      </c>
-      <c r="B22" s="86" t="s">
-        <v>470</v>
-      </c>
-      <c r="C22" s="85" t="s">
-        <v>438</v>
-      </c>
-      <c r="D22" s="86" t="s">
-        <v>434</v>
-      </c>
-      <c r="E22" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" s="86"/>
-      <c r="G22" s="88" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="19.5">
-      <c r="A23" s="86" t="s">
-        <v>471</v>
-      </c>
-      <c r="B23" s="86"/>
-      <c r="C23" s="87" t="s">
-        <v>452</v>
-      </c>
-      <c r="D23" s="86"/>
-      <c r="E23" s="86"/>
-      <c r="F23" s="86"/>
-      <c r="G23" s="88" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.75">
-      <c r="A24" s="86" t="s">
-        <v>472</v>
-      </c>
-      <c r="B24" s="86" t="s">
-        <v>473</v>
-      </c>
-      <c r="C24" s="85" t="s">
-        <v>438</v>
-      </c>
-      <c r="D24" s="86" t="s">
-        <v>434</v>
-      </c>
-      <c r="E24" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="F24" s="86"/>
-      <c r="G24" s="88" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.75">
-      <c r="A25" s="86" t="s">
-        <v>474</v>
-      </c>
-      <c r="B25" s="86" t="s">
-        <v>475</v>
-      </c>
-      <c r="C25" s="85" t="s">
-        <v>438</v>
-      </c>
-      <c r="D25" s="86" t="s">
-        <v>434</v>
-      </c>
-      <c r="E25" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="F25" s="86"/>
-      <c r="G25" s="88" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.75">
-      <c r="A26" s="86" t="s">
-        <v>476</v>
-      </c>
-      <c r="B26" s="86" t="s">
-        <v>477</v>
-      </c>
-      <c r="C26" s="85" t="s">
-        <v>438</v>
-      </c>
-      <c r="D26" s="86" t="s">
-        <v>434</v>
-      </c>
-      <c r="E26" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="F26" s="86"/>
-      <c r="G26" s="88" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.75">
-      <c r="A27" s="86" t="s">
-        <v>478</v>
-      </c>
-      <c r="B27" s="86" t="s">
-        <v>479</v>
-      </c>
-      <c r="C27" s="85" t="s">
-        <v>438</v>
-      </c>
-      <c r="D27" s="86" t="s">
-        <v>434</v>
-      </c>
-      <c r="E27" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27" s="86"/>
-      <c r="G27" s="88" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15.75">
-      <c r="A28" s="90" t="s">
-        <v>480</v>
-      </c>
-      <c r="B28" s="91" t="s">
-        <v>481</v>
-      </c>
-      <c r="C28" s="85" t="s">
-        <v>438</v>
-      </c>
-      <c r="D28" s="91" t="s">
-        <v>434</v>
-      </c>
-      <c r="E28" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="F28" s="93"/>
-      <c r="G28" s="94" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.75">
-      <c r="A29" s="95" t="s">
-        <v>482</v>
-      </c>
-      <c r="B29" s="96" t="s">
-        <v>483</v>
-      </c>
-      <c r="C29" s="85" t="s">
-        <v>438</v>
-      </c>
-      <c r="D29" s="96" t="s">
-        <v>434</v>
-      </c>
-      <c r="E29" s="86" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" s="98"/>
-      <c r="G29" s="99" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="19.5">
-      <c r="A30" s="90" t="s">
-        <v>484</v>
-      </c>
-      <c r="B30" s="93" t="s">
-        <v>485</v>
-      </c>
-      <c r="C30" s="92" t="s">
-        <v>433</v>
-      </c>
-      <c r="D30" s="91" t="s">
-        <v>434</v>
-      </c>
-      <c r="E30" s="93"/>
-      <c r="F30" s="93"/>
-      <c r="G30" s="94" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="19.5">
-      <c r="A31" s="95" t="s">
-        <v>486</v>
-      </c>
-      <c r="B31" s="96" t="s">
-        <v>487</v>
-      </c>
-      <c r="C31" s="97" t="s">
-        <v>433</v>
-      </c>
-      <c r="D31" s="96" t="s">
-        <v>434</v>
-      </c>
-      <c r="E31" s="98"/>
-      <c r="F31" s="98"/>
-      <c r="G31" s="99" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="19.5">
-      <c r="A32" s="90" t="s">
+    </row>
+    <row r="37" spans="1:7" s="66" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C37" s="67"/>
+    </row>
+    <row r="38" spans="1:7" s="66" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C38" s="67"/>
+    </row>
+    <row r="39" spans="1:7" s="66" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C39" s="67"/>
+    </row>
+    <row r="40" spans="1:7" s="66" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="68" t="s">
         <v>488</v>
       </c>
-      <c r="B32" s="93"/>
-      <c r="C32" s="92" t="s">
-        <v>433</v>
-      </c>
-      <c r="D32" s="91" t="s">
-        <v>434</v>
-      </c>
-      <c r="E32" s="93"/>
-      <c r="F32" s="93"/>
-      <c r="G32" s="94" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="19.5">
-      <c r="A33" s="95" t="s">
+      <c r="C40" s="67"/>
+    </row>
+    <row r="41" spans="1:7" s="66" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>489</v>
       </c>
-      <c r="B33" s="98"/>
-      <c r="C33" s="97" t="s">
-        <v>433</v>
-      </c>
-      <c r="D33" s="96" t="s">
-        <v>434</v>
-      </c>
-      <c r="E33" s="98"/>
-      <c r="F33" s="98"/>
-      <c r="G33" s="99" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="19.5">
-      <c r="A34" s="100" t="s">
+      <c r="B41" s="66" t="s">
+        <v>579</v>
+      </c>
+      <c r="C41" s="66" t="s">
+        <v>581</v>
+      </c>
+      <c r="D41" s="66" t="s">
+        <v>583</v>
+      </c>
+      <c r="E41" s="66" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" s="66" customFormat="1" ht="409.6" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>490</v>
       </c>
-      <c r="B34" s="101" t="s">
+      <c r="B42" s="112" t="s">
+        <v>578</v>
+      </c>
+      <c r="C42" s="113" t="s">
+        <v>580</v>
+      </c>
+      <c r="D42" s="112" t="s">
+        <v>582</v>
+      </c>
+      <c r="E42" s="112" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>491</v>
       </c>
-      <c r="C34" s="102" t="s">
-        <v>433</v>
-      </c>
-      <c r="D34" s="91" t="s">
-        <v>434</v>
-      </c>
-      <c r="E34" s="93"/>
-      <c r="F34" s="93"/>
-      <c r="G34" s="94" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="19.5">
-      <c r="A35" s="86" t="s">
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>492</v>
       </c>
-      <c r="B35" s="86"/>
-      <c r="C35" s="87" t="s">
-        <v>452</v>
-      </c>
-      <c r="D35" s="86"/>
-      <c r="E35" s="86"/>
-      <c r="F35" s="86"/>
-      <c r="G35" s="88"/>
-    </row>
-    <row r="36" spans="1:7" ht="19.5">
-      <c r="A36" s="86" t="s">
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>493</v>
       </c>
-      <c r="B36" s="86"/>
-      <c r="C36" s="87" t="s">
-        <v>452</v>
-      </c>
-      <c r="D36" s="86"/>
-      <c r="E36" s="86"/>
-      <c r="F36" s="86"/>
-      <c r="G36" s="88"/>
-    </row>
-    <row r="37" spans="1:7" s="67" customFormat="1">
-      <c r="C37" s="68"/>
-    </row>
-    <row r="38" spans="1:7" s="67" customFormat="1">
-      <c r="C38" s="68"/>
-    </row>
-    <row r="39" spans="1:7" s="67" customFormat="1">
-      <c r="C39" s="68"/>
-    </row>
-    <row r="40" spans="1:7" s="67" customFormat="1">
-      <c r="A40" s="69" t="s">
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>494</v>
       </c>
-      <c r="C40" s="68"/>
-    </row>
-    <row r="41" spans="1:7" s="67" customFormat="1">
-      <c r="A41" t="s">
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>495</v>
       </c>
-      <c r="C41" s="68"/>
-    </row>
-    <row r="42" spans="1:7" s="67" customFormat="1">
-      <c r="A42" t="s">
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>496</v>
       </c>
-      <c r="C42" s="68"/>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
-      <c r="A61" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
-      <c r="A66" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
-      <c r="A69" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A81" s="80" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A82" s="81" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A83" s="82" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A84" s="83" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
-      <c r="A75" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" s="81" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="82" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" s="83" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" s="84" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="85" t="s">
-        <v>438</v>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A85" s="84" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A86" s="103" t="s">
+        <v>573</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C35:C36 C4 C11:C12 C16:C17 C21 C23" xr:uid="{00B600D9-000A-4B4B-9CF8-00B8002E00A1}">
-      <formula1>$U$1:$U$5</formula1>
-    </dataValidation>
-  </dataValidations>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
   </hyperlinks>
@@ -9271,7 +10276,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.28515625" customWidth="1"/>
     <col min="2" max="2" width="19.42578125" customWidth="1"/>
@@ -9282,204 +10287,204 @@
     <col min="7" max="7" width="111.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="69" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="70" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="70" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="72" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B4" s="60" t="s">
+        <v>531</v>
+      </c>
+      <c r="C4" t="s">
+        <v>532</v>
+      </c>
+      <c r="E4" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="73" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="70" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="71" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="71" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="71" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="71" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="73" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="B5" s="60" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
+      <c r="C5" t="s">
         <v>536</v>
       </c>
-      <c r="B4" s="60" t="s">
+      <c r="E5" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="59"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>537</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B6" s="60" t="s">
         <v>538</v>
       </c>
-      <c r="E4" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="74" t="s">
+      <c r="C6" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
+      <c r="E6" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="75"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>540</v>
       </c>
-      <c r="B5" s="60" t="s">
+      <c r="E7" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="74" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="59"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>541</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B8" s="60" t="s">
         <v>542</v>
       </c>
-      <c r="E5" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="59"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
+      <c r="C8" t="s">
         <v>543</v>
       </c>
-      <c r="B6" s="60" t="s">
+      <c r="E8" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="75"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>544</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B9" s="60" t="s">
         <v>545</v>
       </c>
-      <c r="E6" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="76"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
+      <c r="C9" t="s">
         <v>546</v>
       </c>
-      <c r="E7" s="75" t="b">
+      <c r="E9" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="F7" s="75" t="b">
+      <c r="F9" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="G7" s="59"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
+      <c r="G9" s="76" t="s">
         <v>547</v>
       </c>
-      <c r="B8" s="60" t="s">
+      <c r="H9" t="s">
         <v>548</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>549</v>
       </c>
-      <c r="E8" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="76"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
+      <c r="B10" s="60" t="s">
         <v>550</v>
       </c>
-      <c r="B9" s="60" t="s">
+      <c r="C10" t="s">
         <v>551</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E10" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="75"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>552</v>
       </c>
-      <c r="E9" s="75" t="b">
+      <c r="B11" s="60" t="s">
+        <v>553</v>
+      </c>
+      <c r="C11" t="s">
+        <v>554</v>
+      </c>
+      <c r="E11" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="F9" s="75" t="b">
+      <c r="F11" s="74" t="b">
         <v>0</v>
       </c>
-      <c r="G9" s="77" t="s">
-        <v>553</v>
-      </c>
-      <c r="H9" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
+      <c r="G11" s="77" t="s">
         <v>555</v>
       </c>
-      <c r="B10" s="60" t="s">
+      <c r="H11" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>556</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B12" s="60" t="s">
         <v>557</v>
       </c>
-      <c r="E10" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="76"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
+      <c r="C12" t="s">
         <v>558</v>
       </c>
-      <c r="B11" s="60" t="s">
-        <v>559</v>
-      </c>
-      <c r="C11" t="s">
-        <v>560</v>
-      </c>
-      <c r="E11" s="75" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="75" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="78" t="s">
-        <v>561</v>
-      </c>
-      <c r="H11" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>562</v>
-      </c>
-      <c r="B12" s="60" t="s">
-        <v>563</v>
-      </c>
-      <c r="C12" t="s">
-        <v>564</v>
-      </c>
       <c r="E12" s="32" t="b">
         <v>1</v>
       </c>
       <c r="F12" s="32" t="b">
         <v>1</v>
       </c>
-      <c r="G12" s="76"/>
+      <c r="G12" s="75"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -9717,13 +10722,45 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0679E28-9C2F-43C9-A5D3-99B312AE2DCC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0679E28-9C2F-43C9-A5D3-99B312AE2DCC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="74d8dd55-54bf-4050-97cc-7368f41a7402"/>
+    <ds:schemaRef ds:uri="76945eef-d346-4c80-a4df-7c150902d8cc"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0E4FD3E-825C-4877-9ECF-7CAB871B7452}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0E4FD3E-825C-4877-9ECF-7CAB871B7452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70932220-5BB6-4277-BD90-11309A94E85B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70932220-5BB6-4277-BD90-11309A94E85B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="76945eef-d346-4c80-a4df-7c150902d8cc"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="74d8dd55-54bf-4050-97cc-7368f41a7402"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>